--- a/docs/テストケース/PG2-1-01_単体テストケース・結果一覧表_担当者引継ぎ実行.xlsx
+++ b/docs/テストケース/PG2-1-01_単体テストケース・結果一覧表_担当者引継ぎ実行.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="単体テストケース・結果一覧" sheetId="1" r:id="R5412f2c70ddf4983"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="共通条件・参照資料" sheetId="2" r:id="R86ee95729cb442a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仕様確認事項" sheetId="3" r:id="R1c98147659004b69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="単体テストケース・結果一覧" sheetId="1" r:id="R10346f36006b4d48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="共通条件・参照資料" sheetId="2" r:id="Rcf706207bc974ec7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仕様確認事項" sheetId="3" r:id="Rb15549db25f64e3f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3445,616 +3445,247 @@
       <x:c r="M52" s="10"/>
       <x:c r="N52" s="10"/>
     </x:row>
-    <x:row r="53" ht="190" customHeight="1">
+    <x:row r="53" ht="230" customHeight="1">
       <x:c r="A53" s="3" t="n">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B53" s="3" t="str">
-        <x:v>例外・トランザクション</x:v>
+        <x:v>引継元不在・引継先確認</x:v>
       </x:c>
       <x:c r="C53" s="3" t="str">
-        <x:v>1 実行日取得でException</x:v>
+        <x:v>引継元不在・引継先登録済み（過去データFALSE）</x:v>
       </x:c>
       <x:c r="D53" s="3" t="str">
-        <x:v>異常系</x:v>
+        <x:v>正常系</x:v>
       </x:c>
       <x:c r="E53" s="3" t="str">
-        <x:v>引継元：組織ID O0470011／担当者ID U0470011
-引継先：組織ID O0470012／担当者ID U0470012
-引継種別：0（個別）。次の営業担当引継情報を準備する。
-法人番号 9900000047001：予定日2026-10-26、状態1（予定）、過去データFALSE。
-法人番号 9900000047002：予定日2026-10-26、状態1（予定）、過去データFALSE。
-この行の登録日時2026-10-26 00:40:00／更新日時2026-10-26 00:30:00。
-個別記載のない行の登録・更新日時：2026-10-26 00:30:00。実施日時：NULL。
-担当者情報マスタ：法人番号 9900000047001／組織ID O0470011／担当者ID U0470011を1件。
-担当者情報マスタ：法人番号 9900000047002／組織ID O0470011／担当者ID U0470011を1件。
-法人番号 9900000047001の担当者ID U0470012は未登録。
-月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報：対象法人の行は0件。</x:v>
+        <x:v>法人番号：9900000047001。
+引継元：組織ID O0470011／担当者ID U0470011（未登録）。
+引継先：組織ID O0470012／担当者ID U0470012（担当者情報マスタに1件登録済み）。
+営業担当引継情報：上記の元→先を1件。予定日2026-10-26、状態1（予定）、引継種別0（個別）、過去データ引継ぎフラグFALSE。登録・更新日時2026-10-26 00:30:00、実施日時NULL。
+月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報：上記法人・引継元組織で各1件。建物マスタは同意書取得組織、他7表は組織IDに引継元組織を設定。</x:v>
       </x:c>
       <x:c r="F53" s="3" t="str">
-        <x:v>① 前提欄のデータを検証DBに準備し、対象行と非対象行を保存する。
-アプリのテスト用時計を2026-10-26 01:00:00に固定する。OS時計は変更しない。
-例外注入：実行日取得：get_current_timeに例外を注入（ジョブ生成前）。
-日付取得の例外はジョブ生成前に設定する。
-② 次のコマンドで実行する。
-python -m cndx_corp_batch.entrypoints.sales_user_handover_batch
-実行後、担当者情報マスタ・営業担当引継情報・前提欄に記載した過去データの変更内容、件数、ログを予想結果と比較する。
-ロールバック、後続処理の呼出し有無、エラーログも確認する。</x:v>
+        <x:v>① --case 47でテストデータを準備し、引継情報・登録済み担当者・過去データ全行を保存する。
+② リポジトリのルートで実行する。
+python -m cndx_corp_batch.entrypoints.sales_user_handover_batch --batch-date 2026-10-26
+③ 保存した各行と実行後のDBを比較する。担当者マスタを更新・削除しないこと、フラグに応じた過去データ処理と完了更新を確認する。</x:v>
       </x:c>
       <x:c r="G53" s="3" t="str">
-        <x:v>実行日取得失敗により対象取得・法人処理を実行しない。DBセッション開始前なのでDBの変更・ロールバック・状態3の記録は行わない。例外の終了扱い・ログ仕様はQ06を確認する。</x:v>
+        <x:v>法人番号9900000047001の営業担当引継情報1件を残し、状態0（完了）へ更新する。実施日時は処理前後のDB時刻の範囲内。
+担当者情報マスタのO0470012／U0470012は全項目を保持し、元担当者は作成しない。
+月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報は各1件のまま、全項目を保持する。過去データの存在確認・更新は呼び出さない。</x:v>
       </x:c>
       <x:c r="H53" s="3" t="str">
-        <x:v>内容!U9、フロー図 コミット注記、処理結果一覧!A7:D7</x:v>
-      </x:c>
-      <x:c r="I53" s="3" t="str">
-        <x:v>Q06</x:v>
-      </x:c>
+        <x:v>内容!AV60:AV75、更新仕様!A125、追加要件画像（2026-10-26指示）、2026-10-27ユーザー確認</x:v>
+      </x:c>
+      <x:c r="I53" s="3"/>
       <x:c r="J53" s="3" t="str">
-        <x:v>仕様確認待ち</x:v>
+        <x:v>未実施</x:v>
       </x:c>
       <x:c r="K53" s="10"/>
       <x:c r="L53" s="11"/>
       <x:c r="M53" s="10"/>
       <x:c r="N53" s="10"/>
     </x:row>
-    <x:row r="54" ht="190" customHeight="1">
+    <x:row r="54" ht="230" customHeight="1">
       <x:c r="A54" s="9" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B54" s="9" t="str">
-        <x:v>例外・トランザクション</x:v>
+        <x:v>引継元不在・引継先確認</x:v>
       </x:c>
       <x:c r="C54" s="9" t="str">
-        <x:v>2 対象取得でException</x:v>
+        <x:v>引継元不在・引継先登録済み（過去データTRUE）</x:v>
       </x:c>
       <x:c r="D54" s="9" t="str">
-        <x:v>異常系</x:v>
+        <x:v>正常系</x:v>
       </x:c>
       <x:c r="E54" s="9" t="str">
-        <x:v>引継元：組織ID O0480011／担当者ID U0480011
-引継先：組織ID O0480012／担当者ID U0480012
-引継種別：0（個別）。次の営業担当引継情報を準備する。
-法人番号 9900000048001：予定日2026-10-26、状態1（予定）、過去データFALSE。
-法人番号 9900000048002：予定日2026-10-26、状態1（予定）、過去データFALSE。
-この行の登録日時2026-10-26 00:40:00／更新日時2026-10-26 00:30:00。
-個別記載のない行の登録・更新日時：2026-10-26 00:30:00。実施日時：NULL。
-担当者情報マスタ：法人番号 9900000048001／組織ID O0480011／担当者ID U0480011を1件。
-担当者情報マスタ：法人番号 9900000048002／組織ID O0480011／担当者ID U0480011を1件。
-法人番号 9900000048001の担当者ID U0480012は未登録。
-月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報：対象法人の行は0件。</x:v>
+        <x:v>法人番号：9900000048001。
+引継元：組織ID O0480011／担当者ID U0480011（未登録）。
+引継先：組織ID O0480012／担当者ID U0480012（担当者情報マスタに1件登録済み）。
+営業担当引継情報：上記の元→先を1件。予定日2026-10-26、状態1（予定）、引継種別0（個別）、過去データ引継ぎフラグTRUE。登録・更新日時2026-10-26 00:30:00、実施日時NULL。
+月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報：上記法人・引継元組織で各1件。建物マスタは同意書取得組織、他7表は組織IDに引継元組織を設定。</x:v>
       </x:c>
       <x:c r="F54" s="9" t="str">
-        <x:v>① 前提欄のデータを検証DBに準備し、対象行と非対象行を保存する。
-例外注入：対象取得：select_sales_user_handover_targets.sqlの実行に例外を注入。
-② 次のコマンドで実行する。
+        <x:v>① --case 48でテストデータを準備し、引継情報・登録済み担当者・過去データ全行を保存する。
+② リポジトリのルートで実行する。
 python -m cndx_corp_batch.entrypoints.sales_user_handover_batch --batch-date 2026-10-26
-実行後、担当者情報マスタ・営業担当引継情報・前提欄に記載した過去データの変更内容、件数、ログを予想結果と比較する。
-ロールバック、後続処理の呼出し有無、エラーログも確認する。</x:v>
+③ 保存した各行と実行後のDBを比較する。担当者マスタを更新・削除しないこと、フラグに応じた過去データ処理と完了更新を確認する。</x:v>
       </x:c>
       <x:c r="G54" s="9" t="str">
-        <x:v>対象取得が失敗したら法人処理を実行しない。未取得の法人を推測して状態3に更新しない。開始済みトランザクションの扱いと例外終了・ログはQ06を確認する。</x:v>
+        <x:v>法人番号9900000048001の営業担当引継情報1件を残し、状態0（完了）へ更新する。実施日時は処理前後のDB時刻の範囲内。
+担当者情報マスタのO0480012／U0480012は全項目を保持し、元担当者は作成しない。
+月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報は各1件のまま、引継元組織O0480011を引継先組織O0480012へ更新する。建物マスタは同意書取得組織、他7表は組織IDを更新し、それ以外の項目を保持する。</x:v>
       </x:c>
       <x:c r="H54" s="9" t="str">
-        <x:v>内容!U9、フロー図 コミット注記、処理結果一覧!A7:D7</x:v>
-      </x:c>
-      <x:c r="I54" s="9" t="str">
-        <x:v>Q06</x:v>
-      </x:c>
+        <x:v>内容!AV60:AV75、更新仕様!A125、追加要件画像（2026-10-26指示）、2026-10-27ユーザー確認</x:v>
+      </x:c>
+      <x:c r="I54" s="9"/>
       <x:c r="J54" s="9" t="str">
-        <x:v>仕様確認待ち</x:v>
+        <x:v>未実施</x:v>
       </x:c>
       <x:c r="K54" s="10"/>
       <x:c r="L54" s="11"/>
       <x:c r="M54" s="10"/>
       <x:c r="N54" s="10"/>
     </x:row>
-    <x:row r="55" ht="190" customHeight="1">
-      <x:c r="A55" s="3" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B55" s="3" t="str">
-        <x:v>例外・トランザクション</x:v>
-      </x:c>
-      <x:c r="C55" s="3" t="str">
-        <x:v>3 担当者存在確認でException</x:v>
-      </x:c>
-      <x:c r="D55" s="3" t="str">
-        <x:v>異常系</x:v>
-      </x:c>
-      <x:c r="E55" s="3" t="str">
-        <x:v>引継元：組織ID O0490011／担当者ID U0490011
-引継先：組織ID O0490012／担当者ID U0490012
-引継種別：0（個別）。次の営業担当引継情報を準備する。
-法人番号 9900000049001：予定日2026-10-26、状態1（予定）、過去データFALSE。
-法人番号 9900000049002：予定日2026-10-26、状態1（予定）、過去データFALSE。
-この行の登録日時2026-10-26 00:40:00／更新日時2026-10-26 00:30:00。
-個別記載のない行の登録・更新日時：2026-10-26 00:30:00。実施日時：NULL。
-担当者情報マスタ：法人番号 9900000049001／組織ID O0490011／担当者ID U0490011を1件。
-担当者情報マスタ：法人番号 9900000049002／組織ID O0490011／担当者ID U0490011を1件。
-法人番号 9900000049001の担当者ID U0490012は未登録。
-月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報：対象法人の行は0件。</x:v>
-      </x:c>
-      <x:c r="F55" s="3" t="str">
-        <x:v>① 前提欄のデータを検証DBに準備し、対象行と非対象行を保存する。
-例外注入：担当者存在確認：select_handover_source_staff.sqlの実行に例外を注入。
-② 次のコマンドで実行する。
-python -m cndx_corp_batch.entrypoints.sales_user_handover_batch --batch-date 2026-10-26
-実行後、担当者情報マスタ・営業担当引継情報・前提欄に記載した過去データの変更内容、件数、ログを予想結果と比較する。
-ロールバック、後続処理の呼出し有無、エラーログも確認する。</x:v>
-      </x:c>
-      <x:c r="G55" s="3" t="str">
-        <x:v>後続処理をスキップし、開始済みトランザクション範囲内をロールバックする。
-確定済み範囲の扱い・状態3への更新可否はQ06確定後に判定。
-例外内容がログに残る。</x:v>
-      </x:c>
-      <x:c r="H55" s="3" t="str">
-        <x:v>内容!U9、フロー図 コミット注記、処理結果一覧!A7:D7</x:v>
-      </x:c>
-      <x:c r="I55" s="3" t="str">
-        <x:v>Q06</x:v>
-      </x:c>
-      <x:c r="J55" s="3" t="str">
-        <x:v>仕様確認待ち</x:v>
-      </x:c>
+    <x:row r="55" ht="15" customHeight="1">
+      <x:c r="A55" s="3"/>
+      <x:c r="B55" s="3"/>
+      <x:c r="C55" s="3"/>
+      <x:c r="D55" s="3"/>
+      <x:c r="E55" s="3"/>
+      <x:c r="F55" s="3"/>
+      <x:c r="G55" s="3"/>
+      <x:c r="H55" s="3"/>
+      <x:c r="I55" s="3"/>
+      <x:c r="J55" s="3"/>
       <x:c r="K55" s="10"/>
       <x:c r="L55" s="11"/>
       <x:c r="M55" s="10"/>
       <x:c r="N55" s="10"/>
     </x:row>
-    <x:row r="56" ht="190" customHeight="1">
-      <x:c r="A56" s="3" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B56" s="3" t="str">
-        <x:v>例外・トランザクション</x:v>
-      </x:c>
-      <x:c r="C56" s="3" t="str">
-        <x:v>4 担当者更新でException</x:v>
-      </x:c>
-      <x:c r="D56" s="3" t="str">
-        <x:v>異常系</x:v>
-      </x:c>
-      <x:c r="E56" s="3" t="str">
-        <x:v>引継元：組織ID O0500011／担当者ID U0500011
-引継先：組織ID O0500012／担当者ID U0500012
-引継種別：0（個別）。次の営業担当引継情報を準備する。
-法人番号 9900000050001：予定日2026-10-26、状態1（予定）、過去データFALSE。
-法人番号 9900000050002：予定日2026-10-26、状態1（予定）、過去データFALSE。
-この行の登録日時2026-10-26 00:40:00／更新日時2026-10-26 00:30:00。
-個別記載のない行の登録・更新日時：2026-10-26 00:30:00。実施日時：NULL。
-担当者情報マスタ：法人番号 9900000050001／組織ID O0500011／担当者ID U0500011を1件。
-担当者情報マスタ：法人番号 9900000050002／組織ID O0500011／担当者ID U0500011を1件。
-法人番号 9900000050001の担当者ID U0500012は未登録。
-月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報：対象法人の行は0件。</x:v>
-      </x:c>
-      <x:c r="F56" s="3" t="str">
-        <x:v>① 前提欄のデータを検証DBに準備し、対象行と非対象行を保存する。
-例外注入：担当者更新：update_handover_staff.sqlの実行に例外を注入。
-② 次のコマンドで実行する。
-python -m cndx_corp_batch.entrypoints.sales_user_handover_batch --batch-date 2026-10-26
-実行後、担当者情報マスタ・営業担当引継情報・前提欄に記載した過去データの変更内容、件数、ログを予想結果と比較する。
-ロールバック、後続処理の呼出し有無、エラーログも確認する。</x:v>
-      </x:c>
-      <x:c r="G56" s="3" t="str">
-        <x:v>後続処理をスキップし、開始済みトランザクション範囲内をロールバックする。
-確定済み範囲の扱い・状態3への更新可否はQ06確定後に判定。
-例外内容がログに残る。</x:v>
-      </x:c>
-      <x:c r="H56" s="3" t="str">
-        <x:v>内容!U9、フロー図 コミット注記、処理結果一覧!A7:D7</x:v>
-      </x:c>
-      <x:c r="I56" s="3" t="str">
-        <x:v>Q06</x:v>
-      </x:c>
-      <x:c r="J56" s="3" t="str">
-        <x:v>仕様確認待ち</x:v>
-      </x:c>
+    <x:row r="56" ht="15" customHeight="1">
+      <x:c r="A56" s="3"/>
+      <x:c r="B56" s="3"/>
+      <x:c r="C56" s="3"/>
+      <x:c r="D56" s="3"/>
+      <x:c r="E56" s="3"/>
+      <x:c r="F56" s="3"/>
+      <x:c r="G56" s="3"/>
+      <x:c r="H56" s="3"/>
+      <x:c r="I56" s="3"/>
+      <x:c r="J56" s="3"/>
       <x:c r="K56" s="10"/>
       <x:c r="L56" s="11"/>
       <x:c r="M56" s="10"/>
       <x:c r="N56" s="10"/>
     </x:row>
-    <x:row r="57" ht="178" customHeight="1">
-      <x:c r="A57" s="9" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B57" s="9" t="str">
-        <x:v>例外・トランザクション</x:v>
-      </x:c>
-      <x:c r="C57" s="9" t="str">
-        <x:v>5 引継情報削除でException</x:v>
-      </x:c>
-      <x:c r="D57" s="9" t="str">
-        <x:v>異常系</x:v>
-      </x:c>
-      <x:c r="E57" s="9" t="str">
-        <x:v>引継元：組織ID O0510011／担当者ID U0510011
-引継先：組織ID O0510012／担当者ID U0510012
-引継種別：0（個別）。次の営業担当引継情報を準備する。
-法人番号 9900000051001：予定日2026-10-26、状態1（予定）、過去データFALSE。
-法人番号 9900000051002：予定日2026-10-26、状態1（予定）、過去データFALSE。
-この行の元：O0510011／U0510013、先：O0510012／U0510012。
-この行の登録日時2026-10-26 00:40:00／更新日時2026-10-26 00:30:00。
-個別記載のない行の登録・更新日時：2026-10-26 00:30:00。実施日時：NULL。
-担当者情報マスタ：法人番号 9900000051002／組織ID O0510011／担当者ID U0510013を1件。
-法人番号 9900000051001の担当者ID U0510012は未登録。
-月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報：対象法人の行は0件。</x:v>
-      </x:c>
-      <x:c r="F57" s="9" t="str">
-        <x:v>① 前提欄のデータを検証DBに準備し、対象行と非対象行を保存する。
-例外注入：引継情報削除：delete_invalid_sales_user_handover.sqlの実行に例外を注入。
-② 次のコマンドで実行する。
-python -m cndx_corp_batch.entrypoints.sales_user_handover_batch --batch-date 2026-10-26
-実行後、担当者情報マスタ・営業担当引継情報・前提欄に記載した過去データの変更内容、件数、ログを予想結果と比較する。
-ロールバック、後続処理の呼出し有無、エラーログも確認する。</x:v>
-      </x:c>
-      <x:c r="G57" s="9" t="str">
-        <x:v>後続処理をスキップし、開始済みトランザクション範囲内をロールバックする。
-確定済み範囲の扱い・状態3への更新可否はQ06確定後に判定。
-例外内容がログに残る。</x:v>
-      </x:c>
-      <x:c r="H57" s="9" t="str">
-        <x:v>内容!U9、フロー図 コミット注記、処理結果一覧!A7:D7</x:v>
-      </x:c>
-      <x:c r="I57" s="9" t="str">
-        <x:v>Q06</x:v>
-      </x:c>
-      <x:c r="J57" s="9" t="str">
-        <x:v>仕様確認待ち</x:v>
-      </x:c>
+    <x:row r="57" ht="15" customHeight="1">
+      <x:c r="A57" s="9"/>
+      <x:c r="B57" s="9"/>
+      <x:c r="C57" s="9"/>
+      <x:c r="D57" s="9"/>
+      <x:c r="E57" s="9"/>
+      <x:c r="F57" s="9"/>
+      <x:c r="G57" s="9"/>
+      <x:c r="H57" s="9"/>
+      <x:c r="I57" s="9"/>
+      <x:c r="J57" s="9"/>
       <x:c r="K57" s="10"/>
       <x:c r="L57" s="11"/>
       <x:c r="M57" s="10"/>
       <x:c r="N57" s="10"/>
     </x:row>
-    <x:row r="58" ht="202" customHeight="1">
-      <x:c r="A58" s="9" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B58" s="9" t="str">
-        <x:v>例外・トランザクション</x:v>
-      </x:c>
-      <x:c r="C58" s="9" t="str">
-        <x:v>8 過去データ存在確認でException</x:v>
-      </x:c>
-      <x:c r="D58" s="9" t="str">
-        <x:v>異常系</x:v>
-      </x:c>
-      <x:c r="E58" s="9" t="str">
-        <x:v>引継元：組織ID O0520011／担当者ID U0520011
-引継先：組織ID O0520012／担当者ID U0520012
-引継種別：0（個別）。次の営業担当引継情報を準備する。
-法人番号 9900000052001：予定日2026-10-26、状態1（予定）、過去データTRUE。
-法人番号 9900000052002：予定日2026-10-26、状態1（予定）、過去データFALSE。
-この行の登録日時2026-10-26 00:40:00／更新日時2026-10-26 00:30:00。
-個別記載のない行の登録・更新日時：2026-10-26 00:30:00。実施日時：NULL。
-担当者情報マスタ：法人番号 9900000052001／組織ID O0520011／担当者ID U0520011を1件。
-担当者情報マスタ：法人番号 9900000052002／組織ID O0520011／担当者ID U0520011を1件。
-法人番号 9900000052001の担当者ID U0520012は未登録。
-月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報：次の法人・組織ごとに各テーブルへ登録。
-法人番号 9900000052001／組織 O0520011：1件。</x:v>
-      </x:c>
-      <x:c r="F58" s="9" t="str">
-        <x:v>① 前提欄のデータを検証DBに準備し、対象行と非対象行を保存する。
-例外注入：過去データ存在確認：check_handover_data.sqlの実行に例外を注入。
-② 次のコマンドで実行する。
-python -m cndx_corp_batch.entrypoints.sales_user_handover_batch --batch-date 2026-10-26
-実行後、担当者情報マスタ・営業担当引継情報・前提欄に記載した過去データの変更内容、件数、ログを予想結果と比較する。
-ロールバック、後続処理の呼出し有無、エラーログも確認する。</x:v>
-      </x:c>
-      <x:c r="G58" s="9" t="str">
-        <x:v>後続処理をスキップし、開始済みトランザクション範囲内をロールバックする。
-確定済み範囲の扱い・状態3への更新可否はQ06確定後に判定。
-例外内容がログに残る。</x:v>
-      </x:c>
-      <x:c r="H58" s="9" t="str">
-        <x:v>内容!U9、フロー図 コミット注記、処理結果一覧!A7:D7</x:v>
-      </x:c>
-      <x:c r="I58" s="9" t="str">
-        <x:v>Q06</x:v>
-      </x:c>
-      <x:c r="J58" s="9" t="str">
-        <x:v>仕様確認待ち</x:v>
-      </x:c>
+    <x:row r="58" ht="15" customHeight="1">
+      <x:c r="A58" s="9"/>
+      <x:c r="B58" s="9"/>
+      <x:c r="C58" s="9"/>
+      <x:c r="D58" s="9"/>
+      <x:c r="E58" s="9"/>
+      <x:c r="F58" s="9"/>
+      <x:c r="G58" s="9"/>
+      <x:c r="H58" s="9"/>
+      <x:c r="I58" s="9"/>
+      <x:c r="J58" s="9"/>
       <x:c r="K58" s="10"/>
       <x:c r="L58" s="11"/>
       <x:c r="M58" s="10"/>
       <x:c r="N58" s="10"/>
     </x:row>
-    <x:row r="59" ht="202" customHeight="1">
-      <x:c r="A59" s="3" t="n">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B59" s="3" t="str">
-        <x:v>例外・トランザクション</x:v>
-      </x:c>
-      <x:c r="C59" s="3" t="str">
-        <x:v>10 過去データ更新でException</x:v>
-      </x:c>
-      <x:c r="D59" s="3" t="str">
-        <x:v>異常系</x:v>
-      </x:c>
-      <x:c r="E59" s="3" t="str">
-        <x:v>引継元：組織ID O0530011／担当者ID U0530011
-引継先：組織ID O0530012／担当者ID U0530012
-引継種別：0（個別）。次の営業担当引継情報を準備する。
-法人番号 9900000053001：予定日2026-10-26、状態1（予定）、過去データTRUE。
-法人番号 9900000053002：予定日2026-10-26、状態1（予定）、過去データFALSE。
-この行の登録日時2026-10-26 00:40:00／更新日時2026-10-26 00:30:00。
-個別記載のない行の登録・更新日時：2026-10-26 00:30:00。実施日時：NULL。
-担当者情報マスタ：法人番号 9900000053001／組織ID O0530011／担当者ID U0530011を1件。
-担当者情報マスタ：法人番号 9900000053002／組織ID O0530011／担当者ID U0530011を1件。
-法人番号 9900000053001の担当者ID U0530012は未登録。
-月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報：次の法人・組織ごとに各テーブルへ登録。
-法人番号 9900000053001／組織 O0530011：1件。</x:v>
-      </x:c>
-      <x:c r="F59" s="3" t="str">
-        <x:v>① 前提欄のデータを検証DBに準備し、対象行と非対象行を保存する。
-例外注入：過去データ更新：update_handover_cn_application.sqlの実行に例外を注入。
-② 次のコマンドで実行する。
-python -m cndx_corp_batch.entrypoints.sales_user_handover_batch --batch-date 2026-10-26
-実行後、担当者情報マスタ・営業担当引継情報・前提欄に記載した過去データの変更内容、件数、ログを予想結果と比較する。
-ロールバック、後続処理の呼出し有無、エラーログも確認する。</x:v>
-      </x:c>
-      <x:c r="G59" s="3" t="str">
-        <x:v>後続処理をスキップし、開始済みトランザクション範囲内をロールバックする。
-確定済み範囲の扱い・状態3への更新可否はQ06確定後に判定。
-例外内容がログに残る。</x:v>
-      </x:c>
-      <x:c r="H59" s="3" t="str">
-        <x:v>内容!U9、フロー図 コミット注記、処理結果一覧!A7:D7</x:v>
-      </x:c>
-      <x:c r="I59" s="3" t="str">
-        <x:v>Q06</x:v>
-      </x:c>
-      <x:c r="J59" s="3" t="str">
-        <x:v>仕様確認待ち</x:v>
-      </x:c>
+    <x:row r="59" ht="15" customHeight="1">
+      <x:c r="A59" s="3"/>
+      <x:c r="B59" s="3"/>
+      <x:c r="C59" s="3"/>
+      <x:c r="D59" s="3"/>
+      <x:c r="E59" s="3"/>
+      <x:c r="F59" s="3"/>
+      <x:c r="G59" s="3"/>
+      <x:c r="H59" s="3"/>
+      <x:c r="I59" s="3"/>
+      <x:c r="J59" s="3"/>
       <x:c r="K59" s="10"/>
       <x:c r="L59" s="11"/>
       <x:c r="M59" s="10"/>
       <x:c r="N59" s="10"/>
     </x:row>
-    <x:row r="60" ht="190" customHeight="1">
-      <x:c r="A60" s="9" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B60" s="9" t="str">
-        <x:v>例外・トランザクション</x:v>
-      </x:c>
-      <x:c r="C60" s="9" t="str">
-        <x:v>11 完了更新でException</x:v>
-      </x:c>
-      <x:c r="D60" s="9" t="str">
-        <x:v>異常系</x:v>
-      </x:c>
-      <x:c r="E60" s="9" t="str">
-        <x:v>引継元：組織ID O0540011／担当者ID U0540011
-引継先：組織ID O0540012／担当者ID U0540012
-引継種別：0（個別）。次の営業担当引継情報を準備する。
-法人番号 9900000054001：予定日2026-10-26、状態1（予定）、過去データFALSE。
-法人番号 9900000054002：予定日2026-10-26、状態1（予定）、過去データFALSE。
-この行の登録日時2026-10-26 00:40:00／更新日時2026-10-26 00:30:00。
-個別記載のない行の登録・更新日時：2026-10-26 00:30:00。実施日時：NULL。
-担当者情報マスタ：法人番号 9900000054001／組織ID O0540011／担当者ID U0540011を1件。
-担当者情報マスタ：法人番号 9900000054002／組織ID O0540011／担当者ID U0540011を1件。
-法人番号 9900000054001の担当者ID U0540012は未登録。
-月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報：対象法人の行は0件。</x:v>
-      </x:c>
-      <x:c r="F60" s="9" t="str">
-        <x:v>① 前提欄のデータを検証DBに準備し、対象行と非対象行を保存する。
-例外注入：完了更新：update_sales_user_handover_status.sqlの状態0更新に例外を注入。
-② 次のコマンドで実行する。
-python -m cndx_corp_batch.entrypoints.sales_user_handover_batch --batch-date 2026-10-26
-実行後、担当者情報マスタ・営業担当引継情報・前提欄に記載した過去データの変更内容、件数、ログを予想結果と比較する。
-ロールバック、後続処理の呼出し有無、エラーログも確認する。</x:v>
-      </x:c>
-      <x:c r="G60" s="9" t="str">
-        <x:v>後続処理をスキップし、開始済みトランザクション範囲内をロールバックする。
-確定済み範囲の扱い・状態3への更新可否はQ06確定後に判定。
-例外内容がログに残る。</x:v>
-      </x:c>
-      <x:c r="H60" s="9" t="str">
-        <x:v>内容!U9、フロー図 コミット注記、処理結果一覧!A7:D7</x:v>
-      </x:c>
-      <x:c r="I60" s="9" t="str">
-        <x:v>Q06</x:v>
-      </x:c>
-      <x:c r="J60" s="9" t="str">
-        <x:v>仕様確認待ち</x:v>
-      </x:c>
+    <x:row r="60" ht="15" customHeight="1">
+      <x:c r="A60" s="9"/>
+      <x:c r="B60" s="9"/>
+      <x:c r="C60" s="9"/>
+      <x:c r="D60" s="9"/>
+      <x:c r="E60" s="9"/>
+      <x:c r="F60" s="9"/>
+      <x:c r="G60" s="9"/>
+      <x:c r="H60" s="9"/>
+      <x:c r="I60" s="9"/>
+      <x:c r="J60" s="9"/>
       <x:c r="K60" s="10"/>
       <x:c r="L60" s="11"/>
       <x:c r="M60" s="10"/>
       <x:c r="N60" s="10"/>
     </x:row>
-    <x:row r="61" ht="214" customHeight="1">
-      <x:c r="A61" s="3" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B61" s="3" t="str">
-        <x:v>例外・トランザクション</x:v>
-      </x:c>
-      <x:c r="C61" s="3" t="str">
-        <x:v>13 エラー状態更新でException</x:v>
-      </x:c>
-      <x:c r="D61" s="3" t="str">
-        <x:v>異常系</x:v>
-      </x:c>
-      <x:c r="E61" s="3" t="str">
-        <x:v>引継元：組織ID O0550011／担当者ID U0550011
-引継先：組織ID O0550012／担当者ID U0550012
-引継種別：0（個別）。次の営業担当引継情報を準備する。
-法人番号 9900000055001：予定日2026-10-26、状態1（予定）、過去データTRUE。
-法人番号 9900000055002：予定日2026-10-26、状態1（予定）、過去データFALSE。
-この行の登録日時2026-10-26 00:40:00／更新日時2026-10-26 00:30:00。
-個別記載のない行の登録・更新日時：2026-10-26 00:30:00。実施日時：NULL。
-担当者情報マスタ：法人番号 9900000055001／組織ID O0550011／担当者ID U0550011を1件。
-担当者情報マスタ：法人番号 9900000055002／組織ID O0550011／担当者ID U0550011を1件。
-法人番号 9900000055001の担当者ID U0550012は未登録。
-月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・CN対策実施申込情報・建物情報：次の法人・組織ごとに各テーブルへ登録。
-法人番号 9900000055001／組織 O0550011：1件。
-建物マスタ：対象法人の行は0件。</x:v>
-      </x:c>
-      <x:c r="F61" s="3" t="str">
-        <x:v>① 前提欄のデータを検証DBに準備し、対象行と非対象行を保存する。
-例外注入：エラー更新：同SQLの状態3更新に例外を注入。再試行側も含むかを記録する。
-② 次のコマンドで実行する。
-python -m cndx_corp_batch.entrypoints.sales_user_handover_batch --batch-date 2026-10-26
-実行後、担当者情報マスタ・営業担当引継情報・前提欄に記載した過去データの変更内容、件数、ログを予想結果と比較する。
-ロールバック、後続処理の呼出し有無、エラーログも確認する。</x:v>
-      </x:c>
-      <x:c r="G61" s="3" t="str">
-        <x:v>後続処理をスキップし、開始済みトランザクション範囲内をロールバックする。
-確定済み範囲の扱い・状態3への更新可否はQ06確定後に判定。
-例外内容がログに残る。</x:v>
-      </x:c>
-      <x:c r="H61" s="3" t="str">
-        <x:v>内容!U9、フロー図 コミット注記、処理結果一覧!A7:D7</x:v>
-      </x:c>
-      <x:c r="I61" s="3" t="str">
-        <x:v>Q06</x:v>
-      </x:c>
-      <x:c r="J61" s="3" t="str">
-        <x:v>仕様確認待ち</x:v>
-      </x:c>
+    <x:row r="61" ht="15" customHeight="1">
+      <x:c r="A61" s="3"/>
+      <x:c r="B61" s="3"/>
+      <x:c r="C61" s="3"/>
+      <x:c r="D61" s="3"/>
+      <x:c r="E61" s="3"/>
+      <x:c r="F61" s="3"/>
+      <x:c r="G61" s="3"/>
+      <x:c r="H61" s="3"/>
+      <x:c r="I61" s="3"/>
+      <x:c r="J61" s="3"/>
       <x:c r="K61" s="10"/>
       <x:c r="L61" s="11"/>
       <x:c r="M61" s="10"/>
       <x:c r="N61" s="10"/>
     </x:row>
-    <x:row r="62" ht="154" customHeight="1">
-      <x:c r="A62" s="9" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B62" s="9" t="str">
-        <x:v>例外・トランザクション</x:v>
-      </x:c>
-      <x:c r="C62" s="9" t="str">
-        <x:v>COMMIT失敗</x:v>
-      </x:c>
-      <x:c r="D62" s="9" t="str">
-        <x:v>異常系</x:v>
-      </x:c>
-      <x:c r="E62" s="9" t="str">
-        <x:v>引継元：組織ID O0560011／担当者ID U0560011
-引継先：組織ID O0560012／担当者ID U0560012
-引継種別：0（個別）。次の営業担当引継情報を準備する。
-法人番号 9900000056001：予定日2026-10-26、状態1（予定）、過去データTRUE。
-個別記載のない行の登録・更新日時：2026-10-26 00:30:00。実施日時：NULL。
-担当者情報マスタ：法人番号 9900000056001／組織ID O0560011／担当者ID U0560011を1件。
-法人番号 9900000056001の担当者ID U0560012は未登録。
-月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報：次の法人・組織ごとに各テーブルへ登録。
-法人番号 9900000056001／組織 O0560011：1件。</x:v>
-      </x:c>
-      <x:c r="F62" s="9" t="str">
-        <x:v>① 前提欄のデータを検証DBに準備し、対象行と非対象行を保存する。
-例外注入：COMMIT：先頭法人のトランザクション確定に例外を注入。現在の実装は法人単位で確定する。
-② 次のコマンドで実行する。
-python -m cndx_corp_batch.entrypoints.sales_user_handover_batch --batch-date 2026-10-26
-実行後、担当者情報マスタ・営業担当引継情報・前提欄に記載した過去データの変更内容、件数、ログを予想結果と比較する。
-ロールバック、後続処理の呼出し有無、エラーログも確認する。</x:v>
-      </x:c>
-      <x:c r="G62" s="9" t="str">
-        <x:v>失敗したトランザクション範囲をロールバックし、エラーをログ出力する。
-担当者・状態更新の残存範囲はコミット境界確定後に判定する。</x:v>
-      </x:c>
-      <x:c r="H62" s="9" t="str">
-        <x:v>フロー図 コミット注記、処理結果一覧!A7:D7</x:v>
-      </x:c>
-      <x:c r="I62" s="9" t="str">
-        <x:v>Q06</x:v>
-      </x:c>
-      <x:c r="J62" s="9" t="str">
-        <x:v>仕様確認待ち</x:v>
-      </x:c>
+    <x:row r="62" ht="15" customHeight="1">
+      <x:c r="A62" s="9"/>
+      <x:c r="B62" s="9"/>
+      <x:c r="C62" s="9"/>
+      <x:c r="D62" s="9"/>
+      <x:c r="E62" s="9"/>
+      <x:c r="F62" s="9"/>
+      <x:c r="G62" s="9"/>
+      <x:c r="H62" s="9"/>
+      <x:c r="I62" s="9"/>
+      <x:c r="J62" s="9"/>
       <x:c r="K62" s="10"/>
       <x:c r="L62" s="11"/>
       <x:c r="M62" s="10"/>
       <x:c r="N62" s="10"/>
     </x:row>
-    <x:row r="63" ht="230" customHeight="1">
-      <x:c r="A63" s="3" t="n">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B63" s="3" t="str">
-        <x:v>引継元不在・引継先確認</x:v>
-      </x:c>
-      <x:c r="C63" s="3" t="str">
-        <x:v>引継元不在・引継先登録済み（過去データFALSE）</x:v>
-      </x:c>
-      <x:c r="D63" s="3" t="str">
-        <x:v>正常系</x:v>
-      </x:c>
-      <x:c r="E63" s="3" t="str">
-        <x:v>法人番号：9900000057001。
-引継元：組織ID O0570011／担当者ID U0570011（未登録）。
-引継先：組織ID O0570012／担当者ID U0570012（担当者情報マスタに1件登録済み）。
-営業担当引継情報：上記の元→先を1件。予定日2026-10-26、状態1（予定）、引継種別0（個別）、過去データ引継ぎフラグFALSE。登録・更新日時2026-10-26 00:30:00、実施日時NULL。
-月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報：上記法人・引継元組織で各1件。建物マスタは同意書取得組織、他7表は組織IDに引継元組織を設定。</x:v>
-      </x:c>
-      <x:c r="F63" s="3" t="str">
-        <x:v>① --case 57でテストデータを準備し、引継情報・登録済み担当者・過去データ全行を保存する。
-② リポジトリのルートで実行する。
-python -m cndx_corp_batch.entrypoints.sales_user_handover_batch --batch-date 2026-10-26
-③ 保存した各行と実行後のDBを比較する。担当者マスタを更新・削除しないこと、フラグに応じた過去データ処理と完了更新を確認する。</x:v>
-      </x:c>
-      <x:c r="G63" s="3" t="str">
-        <x:v>法人番号9900000057001の営業担当引継情報1件を残し、状態0（完了）へ更新する。実施日時は処理前後のDB時刻の範囲内。
-担当者情報マスタのO0570012／U0570012は全項目を保持し、元担当者は作成しない。
-月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報は各1件のまま、全項目を保持する。過去データの存在確認・更新は呼び出さない。</x:v>
-      </x:c>
-      <x:c r="H63" s="3" t="str">
-        <x:v>内容!AV60:AV75、更新仕様!A125、追加要件画像（2026-10-26指示）、2026-10-27ユーザー確認</x:v>
-      </x:c>
+    <x:row r="63" ht="15" customHeight="1">
+      <x:c r="A63" s="3"/>
+      <x:c r="B63" s="3"/>
+      <x:c r="C63" s="3"/>
+      <x:c r="D63" s="3"/>
+      <x:c r="E63" s="3"/>
+      <x:c r="F63" s="3"/>
+      <x:c r="G63" s="3"/>
+      <x:c r="H63" s="3"/>
       <x:c r="I63" s="3"/>
-      <x:c r="J63" s="3" t="str">
-        <x:v>未実施</x:v>
-      </x:c>
+      <x:c r="J63" s="3"/>
       <x:c r="K63" s="10"/>
       <x:c r="L63" s="11"/>
       <x:c r="M63" s="10"/>
       <x:c r="N63" s="10"/>
     </x:row>
-    <x:row r="64" ht="230" customHeight="1">
-      <x:c r="A64" s="9" t="n">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B64" s="9" t="str">
-        <x:v>引継元不在・引継先確認</x:v>
-      </x:c>
-      <x:c r="C64" s="9" t="str">
-        <x:v>引継元不在・引継先登録済み（過去データTRUE）</x:v>
-      </x:c>
-      <x:c r="D64" s="9" t="str">
-        <x:v>正常系</x:v>
-      </x:c>
-      <x:c r="E64" s="9" t="str">
-        <x:v>法人番号：9900000058001。
-引継元：組織ID O0580011／担当者ID U0580011（未登録）。
-引継先：組織ID O0580012／担当者ID U0580012（担当者情報マスタに1件登録済み）。
-営業担当引継情報：上記の元→先を1件。予定日2026-10-26、状態1（予定）、引継種別0（個別）、過去データ引継ぎフラグTRUE。登録・更新日時2026-10-26 00:30:00、実施日時NULL。
-月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報：上記法人・引継元組織で各1件。建物マスタは同意書取得組織、他7表は組織IDに引継元組織を設定。</x:v>
-      </x:c>
-      <x:c r="F64" s="9" t="str">
-        <x:v>① --case 58でテストデータを準備し、引継情報・登録済み担当者・過去データ全行を保存する。
-② リポジトリのルートで実行する。
-python -m cndx_corp_batch.entrypoints.sales_user_handover_batch --batch-date 2026-10-26
-③ 保存した各行と実行後のDBを比較する。担当者マスタを更新・削除しないこと、フラグに応じた過去データ処理と完了更新を確認する。</x:v>
-      </x:c>
-      <x:c r="G64" s="9" t="str">
-        <x:v>法人番号9900000058001の営業担当引継情報1件を残し、状態0（完了）へ更新する。実施日時は処理前後のDB時刻の範囲内。
-担当者情報マスタのO0580012／U0580012は全項目を保持し、元担当者は作成しない。
-月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報は各1件のまま、引継元組織O0580011を引継先組織O0580012へ更新する。建物マスタは同意書取得組織、他7表は組織IDを更新し、それ以外の項目を保持する。</x:v>
-      </x:c>
-      <x:c r="H64" s="9" t="str">
-        <x:v>内容!AV60:AV75、更新仕様!A125、追加要件画像（2026-10-26指示）、2026-10-27ユーザー確認</x:v>
-      </x:c>
+    <x:row r="64" ht="15" customHeight="1">
+      <x:c r="A64" s="9"/>
+      <x:c r="B64" s="9"/>
+      <x:c r="C64" s="9"/>
+      <x:c r="D64" s="9"/>
+      <x:c r="E64" s="9"/>
+      <x:c r="F64" s="9"/>
+      <x:c r="G64" s="9"/>
+      <x:c r="H64" s="9"/>
       <x:c r="I64" s="9"/>
-      <x:c r="J64" s="9" t="str">
-        <x:v>未実施</x:v>
-      </x:c>
+      <x:c r="J64" s="9"/>
       <x:c r="K64" s="10"/>
       <x:c r="L64" s="11"/>
       <x:c r="M64" s="10"/>
@@ -4174,7 +3805,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47264981b64d4933"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea9663f4d4e74ec1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4203,7 +3834,7 @@
     <x:row r="3" ht="118" customHeight="1">
       <x:c r="A3" s="3" t="str">
         <x:v>各ケースに法人番号・組織ID・担当者ID・テーブル名を直接記載しています。
-2026-10-29に全58ケースへ整理し、番号と準備PGの既定IDを揃えました。設定や開始番号を変更した場合は計画JSONの実値を使用してください。</x:v>
+2026-10-29に全48ケースへ整理し、番号と準備PGの既定IDを揃えました。設定や開始番号を変更した場合は計画JSONの実値を使用してください。</x:v>
       </x:c>
       <x:c r="B3" s="3"/>
     </x:row>
@@ -4243,12 +3874,9 @@
           <x:t xml:space="preserve">テストの進め方</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">検証用DBにケースのデータを準備し、バッチまたは対象処理を実行して、DBとログを確認する。
-例外のケースは、スタブ（処理結果を差し替える仕組み）やデバッガで意図的にエラーを発生させる。
-テスト計画書では手動単体テストの対象。データ準備PGを実行しただけでは、テスト完了にならない。</x:t>
-        </x:is>
+      <x:c r="B8" s="9" t="str">
+        <x:v>検証用DBにケースのデータを準備し、バッチまたは対象処理を実行して、DBとログを確認する。
+テスト計画書では手動単体テストの対象。データ準備PGを実行しただけでは、テスト完了にならない。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="78" customHeight="1">
@@ -4300,7 +3928,7 @@
       <x:c r="B12" s="9" t="str">
         <x:v>法人番号・組織ID・担当者IDは各ケースに直接記載する。
 例：ケース19の法人番号9900000019001、元組織O0190011、元担当者U0190011、先組織O0190012、先担当者U0190012。
-番号は1～58の連番。開始番号の既定値はケース番号×1000＋1。設定を変更した場合は計画JSONの実値を使用する。</x:v>
+番号は1～48の連番。開始番号の既定値はケース番号×1000＋1。設定を変更した場合は計画JSONの実値を使用する。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="46" customHeight="1">
@@ -4821,10 +4449,8 @@
       <x:c r="D11" s="3" t="str">
         <x:v>未存在を0として判定するかを統一する。業務エラーはロールバックなしの規定を維持する。</x:v>
       </x:c>
-      <x:c r="E11" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">38, 39, 40, 52</x:t>
-        </x:is>
+      <x:c r="E11" s="3" t="str">
+        <x:v>38, 39, 40, 46</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
         <x:v>未確認</x:v>
@@ -4836,28 +4462,22 @@
         <x:v>Q06</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>例外時の終了・コミット境界</x:v>
-      </x:c>
-      <x:c r="C12" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">内容U9は「11.終了」だが改訂後の終了は14。図には処理5/10/11/13付近に複数のCOMMITがある。</x:t>
-        </x:is>
+        <x:v>業務エラー後の継続・コミット境界</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="str">
+        <x:v>内容U9の終了記述とフロー図LOOP/COMMITの範囲が明確でない。</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>各トランザクションの開始・終了、Exception時の状態3記録、後続法人の継続可否を確定する。</x:v>
-      </x:c>
-      <x:c r="E12" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62</x:t>
-        </x:is>
+        <x:v>業務エラーにした法人の変更確定範囲と、後続法人を処理するかを確定する。</x:v>
+      </x:c>
+      <x:c r="E12" s="9" t="str">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
         <x:v>未確認</x:v>
       </x:c>
-      <x:c r="G12" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-10-27確認済み：元・先とも不在の場合の「14.終了へ」は該当法人だけの終了で、次の法人を処理する。この回答はException時の継続可否・コミット境界を確定するものではない。</x:t>
-        </x:is>
+      <x:c r="G12" s="10" t="str">
+        <x:v>元・先とも不在の場合は該当法人だけ終了して次の法人へ進むことを2026-10-27に確認済み。業務エラー後の継続は未確認。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
